--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Procedure: Surgery, ResourceType Procedure</t>
+    <t>This StructureDefinition contains the maps for VistA SURGERY (file 130) to FHIR Procedure</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="537">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -808,6 +808,10 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-27:1313: fixed value "387713003" {null}</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -942,10 +946,10 @@
     <t>Procedure.code.text</t>
   </si>
   <si>
+    <t>1343: source value from SURGERY - PRINCIPAL PROCEDURE (#130-26)</t>
+  </si>
+  <si>
     <t>Surg.SurgeryPRE.PrincipalProcedureText</t>
-  </si>
-  <si>
-    <t>1343: source value from SURGERY - PRINCIPAL PROCEDURE (#130-26)</t>
   </si>
   <si>
     <t>Procedure.subject</t>
@@ -975,6 +979,9 @@
   </si>
   <si>
     <t>PID-3</t>
+  </si>
+  <si>
+    <t>1287: reference from SURGERY - PATIENT (#130-.01)</t>
   </si>
   <si>
     <t>Surg.AnesthesiaAgent.PatientIEN
@@ -1006,9 +1013,6 @@
 Surg.SurgORScrubSupportTime.PatientIEN</t>
   </si>
   <si>
-    <t>1287: reference from SURGERY - PATIENT (#130-.01)</t>
-  </si>
-  <si>
     <t>Procedure.encounter</t>
   </si>
   <si>
@@ -1080,6 +1084,9 @@
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>1286: source value from SURGERY - DATE OF OPERATION (#130-.09)</t>
   </si>
   <si>
     <t>Surg.AnesthesiaAgent.SurgeryDateTime
@@ -1120,9 +1127,6 @@
 Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
   </si>
   <si>
-    <t>1286: source value from SURGERY - DATE OF OPERATION (#130-.09)</t>
-  </si>
-  <si>
     <t>Procedure.performed[x]:performedPeriod</t>
   </si>
   <si>
@@ -1173,13 +1177,13 @@
     <t>DR.1</t>
   </si>
   <si>
+    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (#130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+  </si>
+  <si>
     <t>Surg.SurgeryINTRA.BeginOperationDateTime
 Surg.SurgeryPRE.BeginOperationDateTime</t>
   </si>
   <si>
-    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (#130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
-  </si>
-  <si>
     <t>Procedure.performed[x]:performedPeriod.end</t>
   </si>
   <si>
@@ -1205,15 +1209,15 @@
   </si>
   <si>
     <t>DR.2</t>
+  </si>
+  <si>
+    <t>1293: source value from SURGERY - TIME OPERATION ENDS (#130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.EndOperationDateTime
 Surg.SurgeryPRE.EndOperationDateTime</t>
   </si>
   <si>
-    <t>1293: source value from SURGERY - TIME OPERATION ENDS (#130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
-  </si>
-  <si>
     <t>Procedure.recorder</t>
   </si>
   <si>
@@ -1345,10 +1349,10 @@
     <t>ORC-19/PRT-5</t>
   </si>
   <si>
+    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (#130-.57)</t>
+  </si>
+  <si>
     <t>Surg.SurgeryINTRA.FoleyCatheterStaffIEN</t>
-  </si>
-  <si>
-    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (#130-.57)</t>
   </si>
   <si>
     <t>Procedure.performer.onBehalfOf</t>
@@ -1392,12 +1396,12 @@
     <t>FiveWs.where[x]</t>
   </si>
   <si>
+    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (#130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
+  </si>
+  <si>
     <t>Surg.SurgeryINTRA.OperatingRoomIEN</t>
   </si>
   <si>
-    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (#130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
-  </si>
-  <si>
     <t>Procedure.reasonCode</t>
   </si>
   <si>
@@ -1437,10 +1441,10 @@
     <t>Procedure.reasonCode.text</t>
   </si>
   <si>
+    <t>1289: source value from SURGERY - PRINCIPAL PRE-OP DIAGNOSIS (#130-32)</t>
+  </si>
+  <si>
     <t>Surg.SurgeryPRE.PrincipalPreOpDiagnosisText</t>
-  </si>
-  <si>
-    <t>1289: source value from SURGERY - PRINCIPAL PRE-OP DIAGNOSIS (#130-32)</t>
   </si>
   <si>
     <t>Procedure.reasonReference</t>
@@ -1570,6 +1574,10 @@
   </si>
   <si>
     <t>Procedure.complication.coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-25:1296: fixed value "88797001" {null}inv-26:1297: fixed value "22298006" {null}</t>
   </si>
   <si>
     <t>1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
@@ -2095,8 +2103,8 @@
     <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="56.90234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="115.109375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="115.109375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="56.90234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4017,10 +4025,10 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -5200,33 +5208,33 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5252,14 +5260,14 @@
         <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5308,7 +5316,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5326,13 +5334,13 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5343,10 +5351,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5369,19 +5377,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5430,7 +5438,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5448,13 +5456,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5465,10 +5473,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5494,16 +5502,16 @@
         <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5552,7 +5560,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5570,13 +5578,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5587,14 +5595,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5616,14 +5624,14 @@
         <v>195</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5648,13 +5656,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5672,7 +5680,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5687,16 +5695,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5707,10 +5715,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5825,10 +5833,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5945,10 +5953,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6059,18 +6067,18 @@
         <v>231</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6096,16 +6104,16 @@
         <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6154,7 +6162,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6172,31 +6180,31 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6215,13 +6223,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6272,7 +6280,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6287,30 +6295,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6333,16 +6341,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6392,7 +6400,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6407,30 +6415,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6453,16 +6461,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6500,7 +6508,7 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
@@ -6510,7 +6518,7 @@
         <v>221</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6525,16 +6533,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6545,13 +6553,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -6573,16 +6581,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6632,7 +6640,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6647,33 +6655,33 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -6695,16 +6703,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6754,7 +6762,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6769,16 +6777,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6789,10 +6797,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6907,10 +6915,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7027,10 +7035,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7053,16 +7061,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7112,7 +7120,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7121,7 +7129,7 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
@@ -7130,27 +7138,27 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7173,23 +7181,23 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>79</v>
@@ -7234,7 +7242,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7243,7 +7251,7 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
@@ -7252,27 +7260,27 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7295,13 +7303,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7352,7 +7360,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7370,10 +7378,10 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7387,10 +7395,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7413,13 +7421,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7470,7 +7478,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7488,10 +7496,10 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -7505,10 +7513,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7531,13 +7539,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7588,7 +7596,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7603,10 +7611,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7623,10 +7631,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7741,10 +7749,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7861,14 +7869,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7890,10 +7898,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -7948,7 +7956,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7983,10 +7991,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8012,14 +8020,14 @@
         <v>195</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8047,10 +8055,10 @@
         <v>199</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8068,7 +8076,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8083,16 +8091,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8103,10 +8111,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8129,17 +8137,17 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8188,7 +8196,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8203,30 +8211,30 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8249,17 +8257,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8308,7 +8316,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8326,7 +8334,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8343,10 +8351,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8369,17 +8377,17 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8428,7 +8436,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8446,27 +8454,27 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8492,13 +8500,13 @@
         <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8527,10 +8535,10 @@
         <v>199</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8548,7 +8556,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8563,13 +8571,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8583,10 +8591,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8701,10 +8709,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8821,10 +8829,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8943,10 +8951,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8972,16 +8980,16 @@
         <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9030,7 +9038,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9048,27 +9056,27 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9091,16 +9099,16 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9150,7 +9158,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9165,13 +9173,13 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -9185,10 +9193,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9214,13 +9222,13 @@
         <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9249,10 +9257,10 @@
         <v>199</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9270,7 +9278,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9288,13 +9296,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9305,10 +9313,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9334,13 +9342,13 @@
         <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9369,10 +9377,10 @@
         <v>199</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9390,7 +9398,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9408,7 +9416,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9425,10 +9433,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9451,16 +9459,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9510,7 +9518,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9528,7 +9536,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9545,10 +9553,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9574,13 +9582,13 @@
         <v>195</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9609,10 +9617,10 @@
         <v>199</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9630,7 +9638,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9648,7 +9656,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9665,10 +9673,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9783,10 +9791,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9903,10 +9911,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10025,10 +10033,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10143,10 +10151,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10263,10 +10271,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10385,10 +10393,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10505,10 +10513,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10602,33 +10610,33 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>482</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10654,14 +10662,14 @@
         <v>212</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10710,7 +10718,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10728,13 +10736,13 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10745,10 +10753,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10771,19 +10779,19 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10832,7 +10840,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10850,13 +10858,13 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10867,10 +10875,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10896,16 +10904,16 @@
         <v>212</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10954,7 +10962,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10972,13 +10980,13 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10989,10 +10997,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11015,17 +11023,17 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11074,7 +11082,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11092,7 +11100,7 @@
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
@@ -11109,10 +11117,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11138,10 +11146,10 @@
         <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11171,10 +11179,10 @@
         <v>199</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -11192,7 +11200,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11210,7 +11218,7 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
@@ -11227,10 +11235,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11253,13 +11261,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11310,7 +11318,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11325,30 +11333,30 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>79</v>
+        <v>505</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>503</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11371,13 +11379,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11428,7 +11436,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11446,7 +11454,7 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
@@ -11463,10 +11471,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11581,10 +11589,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11701,14 +11709,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11730,10 +11738,10 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>138</v>
@@ -11788,7 +11796,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11823,10 +11831,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11852,10 +11860,10 @@
         <v>195</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11885,10 +11893,10 @@
         <v>113</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -11906,7 +11914,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11924,7 +11932,7 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
@@ -11941,10 +11949,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11967,13 +11975,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12024,7 +12032,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>89</v>
@@ -12042,7 +12050,7 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
@@ -12059,10 +12067,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12085,19 +12093,19 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12146,7 +12154,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12164,7 +12172,7 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
@@ -12181,10 +12189,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12210,13 +12218,13 @@
         <v>195</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12245,10 +12253,10 @@
         <v>199</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12266,7 +12274,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12284,7 +12292,7 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-27:1313: fixed value "387713003" {null}</t>
+inv-33:1313: fixed value = 387713003 {null}</t>
   </si>
   <si>
     <t>./code</t>
@@ -1577,7 +1577,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-25:1296: fixed value "88797001" {null}inv-26:1297: fixed value "22298006" {null}</t>
+inv-31:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-32:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
   </si>
   <si>
     <t>1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-33:1313: fixed value = 387713003 {null}</t>
+inv-31:1313: fixed value = 387713003 {null}</t>
   </si>
   <si>
     <t>./code</t>
@@ -1577,7 +1577,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-31:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-32:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
+inv-29:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-30:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
   </si>
   <si>
     <t>1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-31:1313: fixed value = 387713003 {null}</t>
+inv-33:1313: fixed value = 387713003 {null}</t>
   </si>
   <si>
     <t>./code</t>
@@ -1577,7 +1577,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-29:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-30:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
+inv-31:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-32:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
   </si>
   <si>
     <t>1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,7 +809,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-33:1313: fixed value = 387713003 {null}</t>
+inv-34:1313: fixed value = 387713003 {null}</t>
   </si>
   <si>
     <t>./code</t>
@@ -1577,7 +1577,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-31:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-32:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
+inv-32:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-33:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
   </si>
   <si>
     <t>1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA SURGERY (file 130) to FHIR Procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file SURGERY (#130) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1577,10 +1577,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-32:1296: fixed value = 88797001 if SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-33:1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
-  </si>
-  <si>
-    <t>1297: fixed value = 22298006 if SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
+inv-32:1296: fixed value = 88797001 when SURGERY - STOMA COMPLICATIONS (#130-688) case == ‘Y’ {null}inv-33:1297: fixed value = 22298006 when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’ {null}</t>
+  </si>
+  <si>
+    <t>1297: fixed value = 22298006 when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complication.coding.display</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2174,7 +2174,7 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
-    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED &gt; OPERATING ROOM - (130-.02 &gt; 131.7-) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.OperatingRoomIEN,Surg.SurgeryPOST.OperatingRoomIEN</t>
@@ -2861,7 +2861,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="142.33984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="141.98046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8865" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8865" uniqueCount="794">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -743,7 +743,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1313: fixed value = http://snomed.info/sct#387713003 Surgical procedure</t>
+    <t>1313: fixed value = http://snomed.info/sct#387713003 "Surgical procedure"</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
@@ -1373,7 +1373,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1298-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.167 PERFUSIONIST</t>
+    <t>1298-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.167 "PERFUSIONIST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-0.function.text</t>
@@ -1438,7 +1438,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1330-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.14 PRIMARY SURGEON</t>
+    <t>1330-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.14 "PRIMARY SURGEON"</t>
   </si>
   <si>
     <t>Procedure.performer:va-1.function.text</t>
@@ -1496,7 +1496,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1331-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.15 FIRST ASST</t>
+    <t>1331-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.15 "FIRST ASST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-2.function.text</t>
@@ -1554,7 +1554,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1332-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.16 SECOND ASST</t>
+    <t>1332-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.16 "SECOND ASST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-3.function.text</t>
@@ -1612,7 +1612,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1333-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.164 ATTENDING SURGEON</t>
+    <t>1333-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.164 "ATTENDING SURGEON"</t>
   </si>
   <si>
     <t>Procedure.performer:va-4.function.text</t>
@@ -1670,7 +1670,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1334-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.168 ASST PERFUSIONIST</t>
+    <t>1334-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.168 "ASST PERFUSIONIST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-5.function.text</t>
@@ -1728,7 +1728,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1335-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.18 SKIN PREPPED BY (1)</t>
+    <t>1335-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.18 "SKIN PREPPED BY (1)"</t>
   </si>
   <si>
     <t>Procedure.performer:va-6.function.text</t>
@@ -1786,7 +1786,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1336-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.31 PRINC ANESTHETIST</t>
+    <t>1336-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.31 "PRINC ANESTHETIST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-7.function.text</t>
@@ -1844,7 +1844,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1337-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.32 RELIEF ANESTHETIST</t>
+    <t>1337-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.32 "RELIEF ANESTHETIST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-8.function.text</t>
@@ -1902,7 +1902,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1338-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.33 ASST ANESTHETIST</t>
+    <t>1338-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.33 "ASST ANESTHETIST"</t>
   </si>
   <si>
     <t>Procedure.performer:va-9.function.text</t>
@@ -1960,7 +1960,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1339-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 ANESTHESIOLOGIST SUPVR</t>
+    <t>1339-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 "ANESTHESIOLOGIST SUPVR"</t>
   </si>
   <si>
     <t>Procedure.performer:va-10.function.text</t>
@@ -2018,7 +2018,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1340-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.522 VERIFIER</t>
+    <t>1340-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.522 "VERIFIER"</t>
   </si>
   <si>
     <t>Procedure.performer:va-11.function.text</t>
@@ -2076,7 +2076,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1341-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#123 PROVIDER</t>
+    <t>1341-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#123 "PROVIDER"</t>
   </si>
   <si>
     <t>Procedure.performer:va-12.function.text</t>
@@ -2134,7 +2134,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1342-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.57 FOLEY CATHETER INSERTED BY</t>
+    <t>1342-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.57 "FOLEY CATHETER INSERTED BY"</t>
   </si>
   <si>
     <t>Procedure.performer:va-13.function.text</t>
@@ -2345,10 +2345,18 @@
     <t>Procedure.complication.coding</t>
   </si>
   <si>
-    <t>1297: fixed value = http://snomed.info/sct#22298006 Myocardial infarction (disorder) when SURGERY - MYOCARDIAL INFARCTION (130-258) case == ‘Y’</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ProcedureSurgeryProcedure-1296:if == ‘Y’ then fixed value http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {null}ProcedureSurgeryProcedure-1297:if == ‘Y’ then fixed value http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {null}</t>
+  </si>
+  <si>
+    <t>1297: fixed value = http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" when SURGERY - MYOCARDIAL INFARCTION (130-258) case == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complication.text</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ProcedureSurgeryProcedure-1296-1:if == ‘Y’ then fixed value STOMA COMPLICATIONS {null}ProcedureSurgeryProcedure-1297-1:if == ‘Y’ then fixed value MYOCARDIAL INFARCTION {null}</t>
   </si>
   <si>
     <t>1297-1: fixed value = MYOCARDIAL INFARCTION case == ‘Y’</t>
@@ -2861,7 +2869,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="141.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="143.6640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>
@@ -29278,10 +29286,10 @@
         <v>79</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>101</v>
+        <v>739</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>79</v>
@@ -29301,10 +29309,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29400,10 +29408,10 @@
         <v>79</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>101</v>
+        <v>742</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>79</v>
@@ -29423,10 +29431,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29449,17 +29457,17 @@
         <v>79</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>79</v>
@@ -29508,7 +29516,7 @@
         <v>79</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -29543,10 +29551,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29572,10 +29580,10 @@
         <v>195</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29605,10 +29613,10 @@
         <v>199</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>79</v>
@@ -29626,7 +29634,7 @@
         <v>79</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -29650,7 +29658,7 @@
         <v>79</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>79</v>
@@ -29661,10 +29669,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29687,13 +29695,13 @@
         <v>79</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -29744,7 +29752,7 @@
         <v>79</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -29759,30 +29767,30 @@
         <v>101</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP224" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29808,10 +29816,10 @@
         <v>384</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29862,7 +29870,7 @@
         <v>79</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -29886,7 +29894,7 @@
         <v>79</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>79</v>
@@ -29897,10 +29905,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30015,10 +30023,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30135,10 +30143,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30257,10 +30265,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30286,10 +30294,10 @@
         <v>195</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30319,10 +30327,10 @@
         <v>113</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>79</v>
@@ -30340,7 +30348,7 @@
         <v>79</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -30364,7 +30372,7 @@
         <v>79</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>79</v>
@@ -30375,10 +30383,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30401,13 +30409,13 @@
         <v>79</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -30458,7 +30466,7 @@
         <v>79</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>89</v>
@@ -30482,7 +30490,7 @@
         <v>79</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>79</v>
@@ -30493,10 +30501,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30519,19 +30527,19 @@
         <v>79</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>79</v>
@@ -30580,7 +30588,7 @@
         <v>79</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -30604,7 +30612,7 @@
         <v>79</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AO231" t="s" s="2">
         <v>79</v>
@@ -30615,10 +30623,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30644,13 +30652,13 @@
         <v>195</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -30679,10 +30687,10 @@
         <v>199</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>79</v>
@@ -30700,7 +30708,7 @@
         <v>79</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -30724,7 +30732,7 @@
         <v>79</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AO232" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2346,7 +2346,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ProcedureSurgeryProcedure-1296:if == ‘Y’ then fixed value http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {null}ProcedureSurgeryProcedure-1297:if == ‘Y’ then fixed value http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {null}</t>
+psp-25-1296:130-688: if == ‘Y’ then http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {null}psp-25-1297:130-258: if == ‘Y’ then http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {null}</t>
   </si>
   <si>
     <t>1297: fixed value = http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" when SURGERY - MYOCARDIAL INFARCTION (130-258) case == ‘Y’</t>
@@ -2356,7 +2356,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ProcedureSurgeryProcedure-1296-1:if == ‘Y’ then fixed value STOMA COMPLICATIONS {null}ProcedureSurgeryProcedure-1297-1:if == ‘Y’ then fixed value MYOCARDIAL INFARCTION {null}</t>
+psp-25-1296-1:undefined: if == ‘Y’ then STOMA COMPLICATIONS {null}psp-25-1297-1:undefined: if == ‘Y’ then MYOCARDIAL INFARCTION {null}</t>
   </si>
   <si>
     <t>1297-1: fixed value = MYOCARDIAL INFARCTION case == ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2886,7 +2886,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="143.6640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="800">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -976,9 +976,6 @@
     <t>Surg.SurgeryPRE.PrincipalProcedureText</t>
   </si>
   <si>
-    <t>surgery.name</t>
-  </si>
-  <si>
     <t>Procedure.subject</t>
   </si>
   <si>
@@ -1002,6 +999,9 @@
     <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
   </si>
   <si>
+    <t>Procedure.CodeTableDetail.Procedure.Code</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1033,7 +1033,7 @@
     <t>1285: reference from SURGERY - VISIT (130-.015)</t>
   </si>
   <si>
-    <t>surgery.encounter</t>
+    <t>Procedure.ProcedureExtension.SecondaryVisit</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1096,7 +1096,7 @@
     <t>SPatient.ImplantedProsthesis.SurgeryDateTime,SPatient.OperationsIndication.SurgeryDateTime,Surg.AnesthesiaAgent.SurgeryDateTime,Surg.AnesthesiaBlockSite.SurgeryDateTime,Surg.AnesthesiaTechnique.SurgeryDateTime,Surg.AnesthesiaTestDose.SurgeryDateTime,Surg.ReferringPhysician.SurgeryDateTime,Surg.ReplacementFluidType.SurgeryDateTime,Surg.SurgeryAssistant.SurgeryDateTime,Surg.SurgeryAssistantOther.SurgeryDateTime,Surg.SurgeryDelay.SurgeryDateTime,Surg.SurgeryINTRA.SurgeryDateTime,Surg.SurgeryIrrigation.SurgeryDateTime,Surg.SurgeryMedication.SurgeryDateTime,Surg.SurgeryOccurrenceNonOp.SurgeryDateTime,Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryOtherProcedure.SurgeryDateTime,Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime,Surg.SurgeryPOST.SurgeryDateTime,Surg.SurgeryPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryPRE.SurgeryDateTime,Surg.SurgeryPreOpDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime,Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime,Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime,Surg.SurgeryProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime,Surg.SurgeryProcedureOccurrence.SurgeryDateTime,Surg.SurgeryRequiredBloodProducts.SurgeryDateTime,Surg.SurgeryReturnCase.SurgeryDateTime,Surg.SurgORCircSupport.SurgeryDateTime,Surg.SurgORCircSupportTime.SurgeryDateTime,Surg.SurgORScrubSupport.SurgeryDateTime,Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
   </si>
   <si>
-    <t>surgery.dateTime</t>
+    <t>Procedure.ProcedureTime</t>
   </si>
   <si>
     <t>Procedure.performed[x]:performedPeriod</t>
@@ -1471,7 +1471,7 @@
     <t>Surg.SurgeryINTRA.SurgeonStaffIEN</t>
   </si>
   <si>
-    <t>surgery.provider</t>
+    <t>Procedure.Clinician</t>
   </si>
   <si>
     <t>Procedure.performer:va-1.onBehalfOf</t>
@@ -1646,6 +1646,9 @@
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AttendingSurgeonStaffIEN</t>
+  </si>
+  <si>
+    <t>Procedure.ProcedureExtension.AttendingClinician</t>
   </si>
   <si>
     <t>Procedure.performer:va-4.onBehalfOf</t>
@@ -7068,7 +7071,7 @@
         <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -7085,14 +7088,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -7111,13 +7114,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7168,7 +7171,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>90</v>
@@ -7183,13 +7186,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>316</v>
@@ -15926,7 +15929,7 @@
         <v>519</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>80</v>
+        <v>520</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>415</v>
@@ -15943,7 +15946,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>419</v>
@@ -16066,13 +16069,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>80</v>
@@ -16189,7 +16192,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>394</v>
@@ -16310,7 +16313,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>395</v>
@@ -16433,7 +16436,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>396</v>
@@ -16558,7 +16561,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>401</v>
@@ -16681,7 +16684,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>432</v>
@@ -16802,7 +16805,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>434</v>
@@ -16925,7 +16928,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>436</v>
@@ -16973,7 +16976,7 @@
         <v>80</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>80</v>
@@ -17027,7 +17030,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>80</v>
@@ -17050,7 +17053,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>440</v>
@@ -17098,7 +17101,7 @@
         <v>80</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>80</v>
@@ -17152,7 +17155,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>80</v>
@@ -17175,7 +17178,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>410</v>
@@ -17275,10 +17278,10 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
@@ -17298,7 +17301,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>419</v>
@@ -17421,13 +17424,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>80</v>
@@ -17544,7 +17547,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>394</v>
@@ -17665,7 +17668,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>395</v>
@@ -17788,7 +17791,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>396</v>
@@ -17913,7 +17916,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>401</v>
@@ -18036,7 +18039,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>432</v>
@@ -18157,7 +18160,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>434</v>
@@ -18280,7 +18283,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>436</v>
@@ -18328,7 +18331,7 @@
         <v>80</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>80</v>
@@ -18382,7 +18385,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>80</v>
@@ -18405,7 +18408,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>440</v>
@@ -18453,7 +18456,7 @@
         <v>80</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>80</v>
@@ -18507,7 +18510,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>80</v>
@@ -18530,7 +18533,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>410</v>
@@ -18630,10 +18633,10 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>80</v>
@@ -18653,7 +18656,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>419</v>
@@ -18776,13 +18779,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>80</v>
@@ -18899,7 +18902,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>394</v>
@@ -19020,7 +19023,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>395</v>
@@ -19143,7 +19146,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>396</v>
@@ -19268,7 +19271,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>401</v>
@@ -19391,7 +19394,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>432</v>
@@ -19512,7 +19515,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>434</v>
@@ -19635,7 +19638,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>436</v>
@@ -19683,7 +19686,7 @@
         <v>80</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>80</v>
@@ -19737,7 +19740,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>80</v>
@@ -19760,7 +19763,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>440</v>
@@ -19808,7 +19811,7 @@
         <v>80</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>80</v>
@@ -19862,7 +19865,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>80</v>
@@ -19885,7 +19888,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>410</v>
@@ -19985,10 +19988,10 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>80</v>
@@ -20008,7 +20011,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>419</v>
@@ -20131,13 +20134,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>80</v>
@@ -20254,7 +20257,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>394</v>
@@ -20375,7 +20378,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>395</v>
@@ -20498,7 +20501,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>396</v>
@@ -20623,7 +20626,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>401</v>
@@ -20746,7 +20749,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>432</v>
@@ -20867,7 +20870,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>434</v>
@@ -20990,7 +20993,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>436</v>
@@ -21038,7 +21041,7 @@
         <v>80</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>80</v>
@@ -21092,7 +21095,7 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>80</v>
@@ -21115,7 +21118,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>440</v>
@@ -21163,7 +21166,7 @@
         <v>80</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>80</v>
@@ -21217,7 +21220,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>80</v>
@@ -21240,7 +21243,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>410</v>
@@ -21340,10 +21343,10 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>80</v>
@@ -21363,7 +21366,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>419</v>
@@ -21486,13 +21489,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>80</v>
@@ -21609,7 +21612,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>394</v>
@@ -21730,7 +21733,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>395</v>
@@ -21853,7 +21856,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>396</v>
@@ -21978,7 +21981,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>401</v>
@@ -22101,7 +22104,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>432</v>
@@ -22222,7 +22225,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>434</v>
@@ -22345,7 +22348,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>436</v>
@@ -22393,7 +22396,7 @@
         <v>80</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>80</v>
@@ -22447,7 +22450,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>80</v>
@@ -22470,7 +22473,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>440</v>
@@ -22518,7 +22521,7 @@
         <v>80</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>80</v>
@@ -22572,7 +22575,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>80</v>
@@ -22595,7 +22598,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>410</v>
@@ -22695,10 +22698,10 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>80</v>
@@ -22718,7 +22721,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>419</v>
@@ -22841,13 +22844,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>80</v>
@@ -22964,7 +22967,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>394</v>
@@ -23085,7 +23088,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>395</v>
@@ -23208,7 +23211,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>396</v>
@@ -23333,7 +23336,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>401</v>
@@ -23456,7 +23459,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>432</v>
@@ -23577,7 +23580,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>434</v>
@@ -23700,7 +23703,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>436</v>
@@ -23748,7 +23751,7 @@
         <v>80</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>80</v>
@@ -23802,7 +23805,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>80</v>
@@ -23825,7 +23828,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>440</v>
@@ -23873,7 +23876,7 @@
         <v>80</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>80</v>
@@ -23927,7 +23930,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>80</v>
@@ -23950,7 +23953,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>410</v>
@@ -24050,10 +24053,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>80</v>
@@ -24073,7 +24076,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>419</v>
@@ -24196,13 +24199,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>80</v>
@@ -24319,7 +24322,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>394</v>
@@ -24440,7 +24443,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>395</v>
@@ -24563,7 +24566,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>396</v>
@@ -24688,7 +24691,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>401</v>
@@ -24811,7 +24814,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>432</v>
@@ -24932,7 +24935,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>434</v>
@@ -25055,7 +25058,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>436</v>
@@ -25103,7 +25106,7 @@
         <v>80</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>80</v>
@@ -25157,7 +25160,7 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>80</v>
@@ -25180,7 +25183,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>440</v>
@@ -25228,7 +25231,7 @@
         <v>80</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>80</v>
@@ -25282,7 +25285,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>80</v>
@@ -25305,7 +25308,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>410</v>
@@ -25405,10 +25408,10 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>80</v>
@@ -25428,7 +25431,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>419</v>
@@ -25551,13 +25554,13 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>80</v>
@@ -25674,7 +25677,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>394</v>
@@ -25795,7 +25798,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>395</v>
@@ -25918,7 +25921,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>396</v>
@@ -26043,7 +26046,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>401</v>
@@ -26166,7 +26169,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>432</v>
@@ -26287,7 +26290,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>434</v>
@@ -26410,7 +26413,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>436</v>
@@ -26458,7 +26461,7 @@
         <v>80</v>
       </c>
       <c r="S192" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="T192" t="s" s="2">
         <v>80</v>
@@ -26512,7 +26515,7 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>80</v>
@@ -26535,7 +26538,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>440</v>
@@ -26583,7 +26586,7 @@
         <v>80</v>
       </c>
       <c r="S193" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="T193" t="s" s="2">
         <v>80</v>
@@ -26637,7 +26640,7 @@
         <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>80</v>
@@ -26660,7 +26663,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>410</v>
@@ -26760,10 +26763,10 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>465</v>
@@ -26783,7 +26786,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>419</v>
@@ -26906,13 +26909,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>80</v>
@@ -27029,7 +27032,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>394</v>
@@ -27150,7 +27153,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>395</v>
@@ -27273,7 +27276,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>396</v>
@@ -27398,7 +27401,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>401</v>
@@ -27521,7 +27524,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>432</v>
@@ -27642,7 +27645,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>434</v>
@@ -27765,7 +27768,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>436</v>
@@ -27813,7 +27816,7 @@
         <v>80</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>80</v>
@@ -27867,7 +27870,7 @@
         <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>80</v>
@@ -27890,7 +27893,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>440</v>
@@ -27938,7 +27941,7 @@
         <v>80</v>
       </c>
       <c r="S204" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="T204" t="s" s="2">
         <v>80</v>
@@ -27992,7 +27995,7 @@
         <v>102</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>80</v>
@@ -28015,7 +28018,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>410</v>
@@ -28115,10 +28118,10 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>80</v>
@@ -28138,7 +28141,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>419</v>
@@ -28261,10 +28264,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28287,17 +28290,17 @@
         <v>91</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>80</v>
@@ -28346,7 +28349,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -28361,10 +28364,10 @@
         <v>102</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>80</v>
@@ -28373,10 +28376,10 @@
         <v>80</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AP207" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AQ207" t="s" s="2">
         <v>80</v>
@@ -28384,10 +28387,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28413,13 +28416,13 @@
         <v>196</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -28448,10 +28451,10 @@
         <v>200</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>80</v>
@@ -28469,7 +28472,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28493,13 +28496,13 @@
         <v>80</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AP208" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AQ208" t="s" s="2">
         <v>80</v>
@@ -28507,10 +28510,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28628,10 +28631,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28751,10 +28754,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28876,10 +28879,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28978,10 +28981,10 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>80</v>
@@ -29001,10 +29004,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29027,16 +29030,16 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -29086,7 +29089,7 @@
         <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -29110,13 +29113,13 @@
         <v>80</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AP213" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AQ213" t="s" s="2">
         <v>80</v>
@@ -29124,10 +29127,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29153,13 +29156,13 @@
         <v>196</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -29188,10 +29191,10 @@
         <v>200</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>80</v>
@@ -29209,7 +29212,7 @@
         <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -29236,21 +29239,21 @@
         <v>80</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ214" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29276,13 +29279,13 @@
         <v>196</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -29311,10 +29314,10 @@
         <v>200</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>80</v>
@@ -29332,7 +29335,7 @@
         <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -29359,7 +29362,7 @@
         <v>80</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>80</v>
@@ -29370,10 +29373,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29396,16 +29399,16 @@
         <v>80</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -29455,7 +29458,7 @@
         <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -29482,7 +29485,7 @@
         <v>80</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>80</v>
@@ -29493,10 +29496,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29522,13 +29525,13 @@
         <v>196</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -29557,10 +29560,10 @@
         <v>200</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>80</v>
@@ -29578,7 +29581,7 @@
         <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -29605,7 +29608,7 @@
         <v>80</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>80</v>
@@ -29616,10 +29619,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29737,10 +29740,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29860,10 +29863,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29959,10 +29962,10 @@
         <v>80</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>80</v>
@@ -29985,10 +29988,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30084,10 +30087,10 @@
         <v>80</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>80</v>
@@ -30110,10 +30113,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30136,17 +30139,17 @@
         <v>80</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>80</v>
@@ -30195,7 +30198,7 @@
         <v>80</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -30222,7 +30225,7 @@
         <v>80</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>80</v>
@@ -30233,10 +30236,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30262,10 +30265,10 @@
         <v>196</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -30295,10 +30298,10 @@
         <v>200</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>80</v>
@@ -30316,7 +30319,7 @@
         <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -30343,7 +30346,7 @@
         <v>80</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>80</v>
@@ -30354,10 +30357,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30380,13 +30383,13 @@
         <v>80</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -30437,7 +30440,7 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -30452,7 +30455,7 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>80</v>
@@ -30461,24 +30464,24 @@
         <v>80</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ224" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30504,10 +30507,10 @@
         <v>388</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -30558,7 +30561,7 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30585,7 +30588,7 @@
         <v>80</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>80</v>
@@ -30596,10 +30599,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30717,10 +30720,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30840,10 +30843,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30965,10 +30968,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30994,10 +30997,10 @@
         <v>196</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -31027,10 +31030,10 @@
         <v>114</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>80</v>
@@ -31048,7 +31051,7 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -31075,7 +31078,7 @@
         <v>80</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AP229" t="s" s="2">
         <v>80</v>
@@ -31086,10 +31089,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31112,13 +31115,13 @@
         <v>80</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -31169,7 +31172,7 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>90</v>
@@ -31196,7 +31199,7 @@
         <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -31207,10 +31210,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31233,19 +31236,19 @@
         <v>80</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
@@ -31294,7 +31297,7 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -31321,7 +31324,7 @@
         <v>80</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>80</v>
@@ -31332,10 +31335,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31361,13 +31364,13 @@
         <v>196</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -31396,10 +31399,10 @@
         <v>200</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>80</v>
@@ -31417,7 +31420,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31444,7 +31447,7 @@
         <v>80</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -999,7 +999,7 @@
     <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
   </si>
   <si>
-    <t>Procedure.CodeTableDetail.Procedure.Code</t>
+    <t>Procedure.Procedure[CodeTableDetail.Procedure].Code</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1033,7 +1033,7 @@
     <t>1285: reference from SURGERY - VISIT (130-.015)</t>
   </si>
   <si>
-    <t>Procedure.ProcedureExtension.SecondaryVisit</t>
+    <t>Procedure.Extension[ProcedureExtension].SecondaryVisit</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1648,7 +1648,7 @@
     <t>Surg.SurgeryINTRA.AttendingSurgeonStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.ProcedureExtension.AttendingClinician</t>
+    <t>Procedure.Extension[ProcedureExtension].AttendingClinician</t>
   </si>
   <si>
     <t>Procedure.performer:va-4.onBehalfOf</t>
@@ -2889,7 +2889,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="143.6640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="57.04296875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file SURGERY (130) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file SURGERY (130) to us-core-procedure.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="801">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1235,7 +1235,7 @@
     <t>Limited to "real" people rather than equipment.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -2190,6 +2190,10 @@
   </si>
   <si>
     <t>Ties a procedure to where the records are likely kept.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+psp-25-1294:130-119 &gt; 131.7-: if 130-118 NON-OR PROCEDURE == ‘Y’ then /Location {null}psp-25-1295:130-.02: if 130-118 NON-OR PROCEDURE != ‘Y’ then LocationOR {null}</t>
   </si>
   <si>
     <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
@@ -28361,13 +28365,13 @@
         <v>80</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>102</v>
+        <v>689</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>80</v>
@@ -28376,10 +28380,10 @@
         <v>80</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AP207" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AQ207" t="s" s="2">
         <v>80</v>
@@ -28387,10 +28391,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28416,13 +28420,13 @@
         <v>196</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -28451,10 +28455,10 @@
         <v>200</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>80</v>
@@ -28472,7 +28476,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28496,13 +28500,13 @@
         <v>80</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AP208" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AQ208" t="s" s="2">
         <v>80</v>
@@ -28510,10 +28514,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28631,10 +28635,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28754,10 +28758,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28879,10 +28883,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28981,10 +28985,10 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>80</v>
@@ -29004,10 +29008,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29030,16 +29034,16 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -29089,7 +29093,7 @@
         <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -29113,13 +29117,13 @@
         <v>80</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AP213" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AQ213" t="s" s="2">
         <v>80</v>
@@ -29127,10 +29131,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29156,13 +29160,13 @@
         <v>196</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -29191,10 +29195,10 @@
         <v>200</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>80</v>
@@ -29212,7 +29216,7 @@
         <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -29239,21 +29243,21 @@
         <v>80</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ214" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29279,13 +29283,13 @@
         <v>196</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -29314,10 +29318,10 @@
         <v>200</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>80</v>
@@ -29335,7 +29339,7 @@
         <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -29362,7 +29366,7 @@
         <v>80</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>80</v>
@@ -29373,10 +29377,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29399,16 +29403,16 @@
         <v>80</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -29458,7 +29462,7 @@
         <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -29485,7 +29489,7 @@
         <v>80</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>80</v>
@@ -29496,10 +29500,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29525,13 +29529,13 @@
         <v>196</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -29560,10 +29564,10 @@
         <v>200</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>80</v>
@@ -29581,7 +29585,7 @@
         <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -29608,7 +29612,7 @@
         <v>80</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>80</v>
@@ -29619,10 +29623,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29740,10 +29744,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29863,10 +29867,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29962,10 +29966,10 @@
         <v>80</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>80</v>
@@ -29988,10 +29992,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30087,10 +30091,10 @@
         <v>80</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>80</v>
@@ -30113,10 +30117,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30139,17 +30143,17 @@
         <v>80</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>80</v>
@@ -30198,7 +30202,7 @@
         <v>80</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -30225,7 +30229,7 @@
         <v>80</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>80</v>
@@ -30236,10 +30240,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30265,10 +30269,10 @@
         <v>196</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -30298,10 +30302,10 @@
         <v>200</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>80</v>
@@ -30319,7 +30323,7 @@
         <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -30346,7 +30350,7 @@
         <v>80</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>80</v>
@@ -30357,10 +30361,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30383,13 +30387,13 @@
         <v>80</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -30440,7 +30444,7 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -30455,7 +30459,7 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>80</v>
@@ -30464,24 +30468,24 @@
         <v>80</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ224" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30507,10 +30511,10 @@
         <v>388</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -30561,7 +30565,7 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30588,7 +30592,7 @@
         <v>80</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>80</v>
@@ -30599,10 +30603,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30720,10 +30724,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30843,10 +30847,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30968,10 +30972,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30997,10 +31001,10 @@
         <v>196</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -31030,10 +31034,10 @@
         <v>114</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>80</v>
@@ -31051,7 +31055,7 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -31078,7 +31082,7 @@
         <v>80</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AP229" t="s" s="2">
         <v>80</v>
@@ -31089,10 +31093,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31115,13 +31119,13 @@
         <v>80</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -31172,7 +31176,7 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>90</v>
@@ -31199,7 +31203,7 @@
         <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -31210,10 +31214,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31236,19 +31240,19 @@
         <v>80</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
@@ -31297,7 +31301,7 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -31324,7 +31328,7 @@
         <v>80</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>80</v>
@@ -31335,10 +31339,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31364,13 +31368,13 @@
         <v>196</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -31399,10 +31403,10 @@
         <v>200</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>80</v>
@@ -31420,7 +31424,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31447,7 +31451,7 @@
         <v>80</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="803">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,7 +825,7 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>1344: source value from SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT (130-27 &gt; 81)</t>
+    <t>1344: source value based on SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT (130-27 &gt; 81)</t>
   </si>
   <si>
     <t>Procedure.code.coding.id</t>
@@ -900,7 +900,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1344-1: source value from SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT - CPT CODE (130-27 &gt; 81-.01)</t>
+    <t>1344-1: source value based on SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT - CPT CODE (130-27 &gt; 81-.01)</t>
   </si>
   <si>
     <t>Dim.CPT.CPTCode,Dim.CPT.CPTCode</t>
@@ -927,7 +927,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1344-3: source value from SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT - SHORT NAME (130-27 &gt; 81-2)</t>
+    <t>1344-3: source value based on SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT - SHORT NAME (130-27 &gt; 81-2)</t>
   </si>
   <si>
     <t>Dim.CPT.CPTName,Dim.CPT.CPTName</t>
@@ -970,7 +970,7 @@
     <t>Procedure.code.text</t>
   </si>
   <si>
-    <t>1343: source value from SURGERY - PRINCIPAL PROCEDURE (130-26)</t>
+    <t>1343: source value based on SURGERY - PRINCIPAL PROCEDURE (130-26)</t>
   </si>
   <si>
     <t>Surg.SurgeryPRE.PrincipalProcedureText</t>
@@ -993,7 +993,7 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
-    <t>1287: reference from SURGERY - PATIENT (130-.01)</t>
+    <t>1287: reference based on SURGERY - PATIENT (130-.01)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
@@ -1030,7 +1030,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1285: reference from SURGERY - VISIT (130-.015)</t>
+    <t>1285: reference based on SURGERY - VISIT (130-.015)</t>
   </si>
   <si>
     <t>Procedure.Extension[ProcedureExtension].SecondaryVisit</t>
@@ -1090,7 +1090,7 @@
 </t>
   </si>
   <si>
-    <t>1286: source value from SURGERY - DATE OF OPERATION (130-.09)</t>
+    <t>1286: source value based on SURGERY - DATE OF OPERATION (130-.09)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.SurgeryDateTime,SPatient.OperationsIndication.SurgeryDateTime,Surg.AnesthesiaAgent.SurgeryDateTime,Surg.AnesthesiaBlockSite.SurgeryDateTime,Surg.AnesthesiaTechnique.SurgeryDateTime,Surg.AnesthesiaTestDose.SurgeryDateTime,Surg.ReferringPhysician.SurgeryDateTime,Surg.ReplacementFluidType.SurgeryDateTime,Surg.SurgeryAssistant.SurgeryDateTime,Surg.SurgeryAssistantOther.SurgeryDateTime,Surg.SurgeryDelay.SurgeryDateTime,Surg.SurgeryINTRA.SurgeryDateTime,Surg.SurgeryIrrigation.SurgeryDateTime,Surg.SurgeryMedication.SurgeryDateTime,Surg.SurgeryOccurrenceNonOp.SurgeryDateTime,Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryOtherProcedure.SurgeryDateTime,Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime,Surg.SurgeryPOST.SurgeryDateTime,Surg.SurgeryPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryPRE.SurgeryDateTime,Surg.SurgeryPreOpDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime,Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime,Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime,Surg.SurgeryProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime,Surg.SurgeryProcedureOccurrence.SurgeryDateTime,Surg.SurgeryRequiredBloodProducts.SurgeryDateTime,Surg.SurgeryReturnCase.SurgeryDateTime,Surg.SurgORCircSupport.SurgeryDateTime,Surg.SurgORCircSupportTime.SurgeryDateTime,Surg.SurgORScrubSupport.SurgeryDateTime,Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
@@ -1143,7 +1143,11 @@
 </t>
   </si>
   <si>
-    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+psp-25-1290:If 130-118 NON-OR PROCEDURE == ‘Y’ then source value from (130-121) {null}psp-25-1292:If 130-118 NON-OR PROCEDURE != ‘Y’ then source value from (130-.22) {null}</t>
+  </si>
+  <si>
+    <t>1292: source value based on SURGERY - TIME OPERATION BEGAN (130-.22) if 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.BeginOperationDateTime,Surg.SurgeryPRE.BeginOperationDateTime</t>
@@ -1176,7 +1180,11 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>1293: source value from SURGERY - TIME OPERATION ENDS (130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+psp-25-1291:If 130-118 NON-OR PROCEDURE == ‘Y’ then source value from (130-122) {null}psp-25-1293:If 130-118 NON-OR PROCEDURE != ‘Y’ then source value from (130-.23) {null}</t>
+  </si>
+  <si>
+    <t>1293: source value based on SURGERY - TIME OPERATION ENDS (130-.23) if 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.EndOperationDateTime,Surg.SurgeryPRE.EndOperationDateTime</t>
@@ -1407,7 +1415,7 @@
 </t>
   </si>
   <si>
-    <t>1298: reference from SURGERY - PERFUSIONIST (130-.167)</t>
+    <t>1298: reference based on SURGERY - PERFUSIONIST (130-.167)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.PerfusionistStaffIEN</t>
@@ -1465,7 +1473,7 @@
     <t>Procedure.performer:va-1.actor</t>
   </si>
   <si>
-    <t>1330: reference from SURGERY - PRIMARY SURGEON (130-.14)</t>
+    <t>1330: reference based on SURGERY - PRIMARY SURGEON (130-.14)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.SurgeonStaffIEN</t>
@@ -1526,7 +1534,7 @@
     <t>Procedure.performer:va-2.actor</t>
   </si>
   <si>
-    <t>1331: reference from SURGERY - FIRST ASST (130-.15)</t>
+    <t>1331: reference based on SURGERY - FIRST ASST (130-.15)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.FirstAssistingStaffIEN</t>
@@ -1584,7 +1592,7 @@
     <t>Procedure.performer:va-3.actor</t>
   </si>
   <si>
-    <t>1332: reference from SURGERY - SECOND ASST (130-.16)</t>
+    <t>1332: reference based on SURGERY - SECOND ASST (130-.16)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.SecondAssistingStaffIEN</t>
@@ -1642,7 +1650,7 @@
     <t>Procedure.performer:va-4.actor</t>
   </si>
   <si>
-    <t>1333: reference from SURGERY - ATTENDING SURGEON (130-.164)</t>
+    <t>1333: reference based on SURGERY - ATTENDING SURGEON (130-.164)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AttendingSurgeonStaffIEN</t>
@@ -1703,7 +1711,7 @@
     <t>Procedure.performer:va-5.actor</t>
   </si>
   <si>
-    <t>1334: reference from SURGERY - ASST PERFUSIONIST (130-.168)</t>
+    <t>1334: reference based on SURGERY - ASST PERFUSIONIST (130-.168)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AssistingPerfusionistStaffIEN</t>
@@ -1761,7 +1769,7 @@
     <t>Procedure.performer:va-6.actor</t>
   </si>
   <si>
-    <t>1335: reference from SURGERY - SKIN PREPPED BY (1) (130-.18)</t>
+    <t>1335: reference based on SURGERY - SKIN PREPPED BY (1) (130-.18)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.SkinPreparationStaffIEN</t>
@@ -1819,7 +1827,7 @@
     <t>Procedure.performer:va-7.actor</t>
   </si>
   <si>
-    <t>1336: reference from SURGERY - PRINC ANESTHETIST (130-.31)</t>
+    <t>1336: reference based on SURGERY - PRINC ANESTHETIST (130-.31)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.PrincipalAnesthetistStaffIEN</t>
@@ -1877,7 +1885,7 @@
     <t>Procedure.performer:va-8.actor</t>
   </si>
   <si>
-    <t>1337: reference from SURGERY - RELIEF ANESTHETIST (130-.32)</t>
+    <t>1337: reference based on SURGERY - RELIEF ANESTHETIST (130-.32)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.ReliefAnesthetistStaffIEN</t>
@@ -1935,7 +1943,7 @@
     <t>Procedure.performer:va-9.actor</t>
   </si>
   <si>
-    <t>1338: reference from SURGERY - ASST ANESTHETIST (130-.33)</t>
+    <t>1338: reference based on SURGERY - ASST ANESTHETIST (130-.33)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AssistingAnesthetistStaffIEN</t>
@@ -1993,7 +2001,7 @@
     <t>Procedure.performer:va-10.actor</t>
   </si>
   <si>
-    <t>1339: reference from SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
+    <t>1339: reference based on SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AnesthesiologistSupervisorStaffIEN</t>
@@ -2051,7 +2059,7 @@
     <t>Procedure.performer:va-11.actor</t>
   </si>
   <si>
-    <t>1340: reference from SURGERY - VERIFIER (130-.522)</t>
+    <t>1340: reference based on SURGERY - VERIFIER (130-.522)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.VerifierStaffIEN</t>
@@ -2109,7 +2117,7 @@
     <t>Procedure.performer:va-12.actor</t>
   </si>
   <si>
-    <t>1341: reference from SURGERY - PROVIDER (130-123)</t>
+    <t>1341: reference based on SURGERY - PROVIDER (130-123)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.ProviderIEN</t>
@@ -2167,7 +2175,7 @@
     <t>Procedure.performer:va-13.actor</t>
   </si>
   <si>
-    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (130-.57)</t>
+    <t>1342: reference based on SURGERY - FOLEY CATHETER INSERTED BY (130-.57)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.FoleyCatheterStaffIEN</t>
@@ -2193,10 +2201,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1294:130-119 &gt; 131.7-: if 130-118 NON-OR PROCEDURE == ‘Y’ then /Location {null}psp-25-1295:130-.02: if 130-118 NON-OR PROCEDURE != ‘Y’ then LocationOR {null}</t>
-  </si>
-  <si>
-    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+psp-25-1294:If 130-118 NON-OR PROCEDURE == ‘Y’ then reference /Location based on (130-119 &gt; 131.7-) {null}psp-25-1295:If 130-118 NON-OR PROCEDURE != ‘Y’ then reference LocationOR based on (130-.02) {null}</t>
+  </si>
+  <si>
+    <t>1295: reference based on SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) if 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.OperatingRoomIEN,Surg.SurgeryPOST.OperatingRoomIEN</t>
@@ -2247,7 +2255,7 @@
     <t>Procedure.reasonCode.text</t>
   </si>
   <si>
-    <t>1289: source value from SURGERY - PRINCIPAL PRE-OP DIAGNOSIS (130-32)</t>
+    <t>1289: source value based on SURGERY - PRINCIPAL PRE-OP DIAGNOSIS (130-32)</t>
   </si>
   <si>
     <t>Surg.SurgeryPRE.PrincipalPreOpDiagnosisText</t>
@@ -2368,20 +2376,20 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1296:130-688: if == ‘Y’ then http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {null}psp-25-1297:130-258: if == ‘Y’ then http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {null}</t>
-  </si>
-  <si>
-    <t>1297: fixed value = http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" when SURGERY - MYOCARDIAL INFARCTION (130-258) case == ‘Y’</t>
+psp-25-1296:If (130-688) is == ‘Y’ then fixed value http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {null}psp-25-1297:If (130-258) is == ‘Y’ then fixed value http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {null}</t>
+  </si>
+  <si>
+    <t>1297: fixed value = http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" when SURGERY - MYOCARDIAL INFARCTION (130-258) if == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complication.text</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1296-1:undefined: if == ‘Y’ then STOMA COMPLICATIONS {null}psp-25-1297-1:undefined: if == ‘Y’ then MYOCARDIAL INFARCTION {null}</t>
-  </si>
-  <si>
-    <t>1297-1: fixed value = MYOCARDIAL INFARCTION case == ‘Y’</t>
+psp-25-1296-1:If (undefined) is == ‘Y’ then fixed value STOMA COMPLICATIONS {null}psp-25-1297-1:If (undefined) is == ‘Y’ then fixed value MYOCARDIAL INFARCTION {null}</t>
+  </si>
+  <si>
+    <t>1297-1: fixed value = MYOCARDIAL INFARCTION if == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complicationDetail</t>
@@ -2431,7 +2439,7 @@
     <t>Any other notes and comments about the procedure.</t>
   </si>
   <si>
-    <t>1288: source value from SURGERY - GENERAL COMMENTS (130-.28)</t>
+    <t>1288: source value based on SURGERY - GENERAL COMMENTS (130-.28)</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2891,7 +2899,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="143.6640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="140.60546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="57.04296875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -8048,13 +8056,13 @@
         <v>360</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>361</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -8063,21 +8071,21 @@
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8103,20 +8111,20 @@
         <v>343</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>80</v>
@@ -8161,7 +8169,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -8173,13 +8181,13 @@
         <v>360</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>373</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -8188,21 +8196,21 @@
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8225,13 +8233,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8282,7 +8290,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -8309,10 +8317,10 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -8320,10 +8328,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8346,13 +8354,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8403,7 +8411,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8430,10 +8438,10 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -8441,10 +8449,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8467,13 +8475,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8512,7 +8520,7 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8522,7 +8530,7 @@
         <v>222</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8546,10 +8554,10 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -8560,10 +8568,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8681,10 +8689,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8804,14 +8812,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8833,10 +8841,10 @@
         <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>139</v>
@@ -8891,7 +8899,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8929,10 +8937,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8958,14 +8966,14 @@
         <v>196</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8993,10 +9001,10 @@
         <v>200</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -9014,7 +9022,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9038,24 +9046,24 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9078,17 +9086,17 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -9137,7 +9145,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>90</v>
@@ -9161,24 +9169,24 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9201,17 +9209,17 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -9260,7 +9268,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9287,7 +9295,7 @@
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -9298,13 +9306,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>80</v>
@@ -9326,13 +9334,13 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9383,7 +9391,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9407,10 +9415,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -9421,10 +9429,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9542,10 +9550,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9665,14 +9673,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9694,10 +9702,10 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>139</v>
@@ -9752,7 +9760,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9790,10 +9798,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9819,14 +9827,14 @@
         <v>196</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9854,10 +9862,10 @@
         <v>200</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -9875,7 +9883,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9899,24 +9907,24 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10034,10 +10042,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10157,10 +10165,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10205,7 +10213,7 @@
         <v>80</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>80</v>
@@ -10259,7 +10267,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
@@ -10282,10 +10290,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10330,7 +10338,7 @@
         <v>80</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>80</v>
@@ -10384,7 +10392,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>80</v>
@@ -10407,10 +10415,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10433,17 +10441,17 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -10492,7 +10500,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>90</v>
@@ -10507,33 +10515,33 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10556,17 +10564,17 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -10615,7 +10623,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10642,7 +10650,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10653,13 +10661,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>80</v>
@@ -10681,13 +10689,13 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10738,7 +10746,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10762,10 +10770,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10776,10 +10784,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10897,10 +10905,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11020,14 +11028,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -11049,10 +11057,10 @@
         <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>139</v>
@@ -11107,7 +11115,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11145,10 +11153,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11174,14 +11182,14 @@
         <v>196</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -11209,10 +11217,10 @@
         <v>200</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -11230,7 +11238,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11254,24 +11262,24 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11389,10 +11397,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11512,10 +11520,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11560,7 +11568,7 @@
         <v>80</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>80</v>
@@ -11614,7 +11622,7 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>80</v>
@@ -11637,10 +11645,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11685,7 +11693,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -11739,7 +11747,7 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>80</v>
@@ -11762,10 +11770,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11788,17 +11796,17 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11847,7 +11855,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>90</v>
@@ -11862,33 +11870,33 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11911,17 +11919,17 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11970,7 +11978,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11997,7 +12005,7 @@
         <v>80</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>80</v>
@@ -12008,13 +12016,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>80</v>
@@ -12036,13 +12044,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12093,7 +12101,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12117,10 +12125,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -12131,10 +12139,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12252,10 +12260,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12375,14 +12383,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12404,10 +12412,10 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>139</v>
@@ -12462,7 +12470,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12500,10 +12508,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12529,14 +12537,14 @@
         <v>196</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -12564,10 +12572,10 @@
         <v>200</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -12585,7 +12593,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12609,24 +12617,24 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12744,10 +12752,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12867,10 +12875,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12915,7 +12923,7 @@
         <v>80</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>80</v>
@@ -12969,7 +12977,7 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>80</v>
@@ -12992,10 +13000,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13040,7 +13048,7 @@
         <v>80</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>80</v>
@@ -13094,7 +13102,7 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>80</v>
@@ -13117,10 +13125,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13143,17 +13151,17 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -13202,7 +13210,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>90</v>
@@ -13217,33 +13225,33 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13266,17 +13274,17 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -13325,7 +13333,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13352,7 +13360,7 @@
         <v>80</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -13363,13 +13371,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>80</v>
@@ -13391,13 +13399,13 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13448,7 +13456,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13472,10 +13480,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -13486,10 +13494,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13607,10 +13615,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13730,14 +13738,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13759,10 +13767,10 @@
         <v>136</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>139</v>
@@ -13817,7 +13825,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13855,10 +13863,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13884,14 +13892,14 @@
         <v>196</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13919,10 +13927,10 @@
         <v>200</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13940,7 +13948,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13964,24 +13972,24 @@
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14099,10 +14107,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14222,10 +14230,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14270,7 +14278,7 @@
         <v>80</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>80</v>
@@ -14324,7 +14332,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>80</v>
@@ -14347,10 +14355,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14395,7 +14403,7 @@
         <v>80</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>80</v>
@@ -14449,7 +14457,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>80</v>
@@ -14472,10 +14480,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14498,17 +14506,17 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -14557,7 +14565,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>90</v>
@@ -14572,33 +14580,33 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14621,17 +14629,17 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14680,7 +14688,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14707,7 +14715,7 @@
         <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>80</v>
@@ -14718,13 +14726,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>80</v>
@@ -14746,13 +14754,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14803,7 +14811,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14827,10 +14835,10 @@
         <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>80</v>
@@ -14841,10 +14849,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14962,10 +14970,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15085,14 +15093,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -15114,10 +15122,10 @@
         <v>136</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>139</v>
@@ -15172,7 +15180,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15210,10 +15218,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15239,14 +15247,14 @@
         <v>196</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -15274,10 +15282,10 @@
         <v>200</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -15295,7 +15303,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15319,24 +15327,24 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15454,10 +15462,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15577,10 +15585,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15625,7 +15633,7 @@
         <v>80</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>80</v>
@@ -15679,7 +15687,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>80</v>
@@ -15702,10 +15710,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15750,7 +15758,7 @@
         <v>80</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>80</v>
@@ -15804,7 +15812,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>80</v>
@@ -15827,10 +15835,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15853,17 +15861,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15912,7 +15920,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>90</v>
@@ -15927,33 +15935,33 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15976,17 +15984,17 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -16035,7 +16043,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16062,7 +16070,7 @@
         <v>80</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>80</v>
@@ -16073,13 +16081,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>80</v>
@@ -16101,13 +16109,13 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16158,7 +16166,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16182,10 +16190,10 @@
         <v>80</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>80</v>
@@ -16196,10 +16204,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16317,10 +16325,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16440,14 +16448,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16469,10 +16477,10 @@
         <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>139</v>
@@ -16527,7 +16535,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16565,10 +16573,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16594,14 +16602,14 @@
         <v>196</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -16629,10 +16637,10 @@
         <v>200</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>80</v>
@@ -16650,7 +16658,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16674,24 +16682,24 @@
         <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16809,10 +16817,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16932,10 +16940,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16980,7 +16988,7 @@
         <v>80</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>80</v>
@@ -17034,7 +17042,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>80</v>
@@ -17057,10 +17065,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17105,7 +17113,7 @@
         <v>80</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>80</v>
@@ -17159,7 +17167,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>80</v>
@@ -17182,10 +17190,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17208,17 +17216,17 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -17267,7 +17275,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>90</v>
@@ -17282,33 +17290,33 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17331,17 +17339,17 @@
         <v>80</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>80</v>
@@ -17390,7 +17398,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17417,7 +17425,7 @@
         <v>80</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>80</v>
@@ -17428,13 +17436,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>80</v>
@@ -17456,13 +17464,13 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17513,7 +17521,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17537,10 +17545,10 @@
         <v>80</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>80</v>
@@ -17551,10 +17559,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17672,10 +17680,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17795,14 +17803,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -17824,10 +17832,10 @@
         <v>136</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>139</v>
@@ -17882,7 +17890,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17920,10 +17928,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17949,14 +17957,14 @@
         <v>196</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17984,10 +17992,10 @@
         <v>200</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>80</v>
@@ -18005,7 +18013,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18029,24 +18037,24 @@
         <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18164,10 +18172,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18287,10 +18295,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18335,7 +18343,7 @@
         <v>80</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>80</v>
@@ -18389,7 +18397,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>80</v>
@@ -18412,10 +18420,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18460,7 +18468,7 @@
         <v>80</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>80</v>
@@ -18514,7 +18522,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>80</v>
@@ -18537,10 +18545,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18563,17 +18571,17 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -18622,7 +18630,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>90</v>
@@ -18637,33 +18645,33 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18686,17 +18694,17 @@
         <v>80</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>80</v>
@@ -18745,7 +18753,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18772,7 +18780,7 @@
         <v>80</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>80</v>
@@ -18783,13 +18791,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>80</v>
@@ -18811,13 +18819,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18868,7 +18876,7 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18892,10 +18900,10 @@
         <v>80</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>80</v>
@@ -18906,10 +18914,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19027,10 +19035,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19150,14 +19158,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19179,10 +19187,10 @@
         <v>136</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>139</v>
@@ -19237,7 +19245,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19275,10 +19283,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19304,14 +19312,14 @@
         <v>196</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>80</v>
@@ -19339,10 +19347,10 @@
         <v>200</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>80</v>
@@ -19360,7 +19368,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19384,24 +19392,24 @@
         <v>80</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19519,10 +19527,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19642,10 +19650,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19690,7 +19698,7 @@
         <v>80</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>80</v>
@@ -19744,7 +19752,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>80</v>
@@ -19767,10 +19775,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19815,7 +19823,7 @@
         <v>80</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>80</v>
@@ -19869,7 +19877,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>80</v>
@@ -19892,10 +19900,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19918,17 +19926,17 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>80</v>
@@ -19977,7 +19985,7 @@
         <v>80</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>90</v>
@@ -19992,33 +20000,33 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20041,17 +20049,17 @@
         <v>80</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>80</v>
@@ -20100,7 +20108,7 @@
         <v>80</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20127,7 +20135,7 @@
         <v>80</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>80</v>
@@ -20138,13 +20146,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>80</v>
@@ -20166,13 +20174,13 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -20223,7 +20231,7 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -20247,10 +20255,10 @@
         <v>80</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>80</v>
@@ -20261,10 +20269,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20382,10 +20390,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20505,14 +20513,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -20534,10 +20542,10 @@
         <v>136</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>139</v>
@@ -20592,7 +20600,7 @@
         <v>80</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -20630,10 +20638,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20659,14 +20667,14 @@
         <v>196</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>80</v>
@@ -20694,10 +20702,10 @@
         <v>200</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>80</v>
@@ -20715,7 +20723,7 @@
         <v>80</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20739,24 +20747,24 @@
         <v>80</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20874,10 +20882,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20997,10 +21005,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21045,7 +21053,7 @@
         <v>80</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>80</v>
@@ -21099,7 +21107,7 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>80</v>
@@ -21122,10 +21130,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21170,7 +21178,7 @@
         <v>80</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>80</v>
@@ -21224,7 +21232,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>80</v>
@@ -21247,10 +21255,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21273,17 +21281,17 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>80</v>
@@ -21332,7 +21340,7 @@
         <v>80</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>90</v>
@@ -21347,33 +21355,33 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21396,17 +21404,17 @@
         <v>80</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>80</v>
@@ -21455,7 +21463,7 @@
         <v>80</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -21482,7 +21490,7 @@
         <v>80</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>80</v>
@@ -21493,13 +21501,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>80</v>
@@ -21521,13 +21529,13 @@
         <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21578,7 +21586,7 @@
         <v>80</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21602,10 +21610,10 @@
         <v>80</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>80</v>
@@ -21616,10 +21624,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21737,10 +21745,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21860,14 +21868,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21889,10 +21897,10 @@
         <v>136</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>139</v>
@@ -21947,7 +21955,7 @@
         <v>80</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21985,10 +21993,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22014,14 +22022,14 @@
         <v>196</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>80</v>
@@ -22049,10 +22057,10 @@
         <v>200</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>80</v>
@@ -22070,7 +22078,7 @@
         <v>80</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -22094,24 +22102,24 @@
         <v>80</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22229,10 +22237,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22352,10 +22360,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22400,7 +22408,7 @@
         <v>80</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>80</v>
@@ -22454,7 +22462,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>80</v>
@@ -22477,10 +22485,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22525,7 +22533,7 @@
         <v>80</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>80</v>
@@ -22579,7 +22587,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>80</v>
@@ -22602,10 +22610,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22628,17 +22636,17 @@
         <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>80</v>
@@ -22687,7 +22695,7 @@
         <v>80</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>90</v>
@@ -22702,33 +22710,33 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22751,17 +22759,17 @@
         <v>80</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>80</v>
@@ -22810,7 +22818,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22837,7 +22845,7 @@
         <v>80</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>80</v>
@@ -22848,13 +22856,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>80</v>
@@ -22876,13 +22884,13 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -22933,7 +22941,7 @@
         <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22957,10 +22965,10 @@
         <v>80</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>80</v>
@@ -22971,10 +22979,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23092,10 +23100,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23215,14 +23223,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -23244,10 +23252,10 @@
         <v>136</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N166" t="s" s="2">
         <v>139</v>
@@ -23302,7 +23310,7 @@
         <v>80</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23340,10 +23348,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23369,14 +23377,14 @@
         <v>196</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>80</v>
@@ -23404,10 +23412,10 @@
         <v>200</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>80</v>
@@ -23425,7 +23433,7 @@
         <v>80</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23449,24 +23457,24 @@
         <v>80</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23584,10 +23592,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23707,10 +23715,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23755,7 +23763,7 @@
         <v>80</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>80</v>
@@ -23809,7 +23817,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>80</v>
@@ -23832,10 +23840,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23880,7 +23888,7 @@
         <v>80</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>80</v>
@@ -23934,7 +23942,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>80</v>
@@ -23957,10 +23965,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23983,17 +23991,17 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>80</v>
@@ -24042,7 +24050,7 @@
         <v>80</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>90</v>
@@ -24057,33 +24065,33 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24106,17 +24114,17 @@
         <v>80</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>80</v>
@@ -24165,7 +24173,7 @@
         <v>80</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24192,7 +24200,7 @@
         <v>80</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>80</v>
@@ -24203,13 +24211,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>80</v>
@@ -24231,13 +24239,13 @@
         <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -24288,7 +24296,7 @@
         <v>80</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24312,10 +24320,10 @@
         <v>80</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP174" t="s" s="2">
         <v>80</v>
@@ -24326,10 +24334,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24447,10 +24455,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24570,14 +24578,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -24599,10 +24607,10 @@
         <v>136</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>139</v>
@@ -24657,7 +24665,7 @@
         <v>80</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -24695,10 +24703,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24724,14 +24732,14 @@
         <v>196</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>80</v>
@@ -24759,10 +24767,10 @@
         <v>200</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>80</v>
@@ -24780,7 +24788,7 @@
         <v>80</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24804,24 +24812,24 @@
         <v>80</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ178" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24939,10 +24947,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25062,10 +25070,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25110,7 +25118,7 @@
         <v>80</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>80</v>
@@ -25164,7 +25172,7 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>80</v>
@@ -25187,10 +25195,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25235,7 +25243,7 @@
         <v>80</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>80</v>
@@ -25289,7 +25297,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>80</v>
@@ -25312,10 +25320,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25338,17 +25346,17 @@
         <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>80</v>
@@ -25397,7 +25405,7 @@
         <v>80</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>90</v>
@@ -25412,33 +25420,33 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25461,17 +25469,17 @@
         <v>80</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>80</v>
@@ -25520,7 +25528,7 @@
         <v>80</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25547,7 +25555,7 @@
         <v>80</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>80</v>
@@ -25558,13 +25566,13 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>80</v>
@@ -25586,13 +25594,13 @@
         <v>91</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -25643,7 +25651,7 @@
         <v>80</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25667,10 +25675,10 @@
         <v>80</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>80</v>
@@ -25681,10 +25689,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25802,10 +25810,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25925,14 +25933,14 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -25954,10 +25962,10 @@
         <v>136</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>139</v>
@@ -26012,7 +26020,7 @@
         <v>80</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -26050,10 +26058,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26079,14 +26087,14 @@
         <v>196</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>80</v>
@@ -26114,10 +26122,10 @@
         <v>200</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>80</v>
@@ -26135,7 +26143,7 @@
         <v>80</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -26159,24 +26167,24 @@
         <v>80</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ189" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26294,10 +26302,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26417,10 +26425,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26465,7 +26473,7 @@
         <v>80</v>
       </c>
       <c r="S192" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="T192" t="s" s="2">
         <v>80</v>
@@ -26519,7 +26527,7 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>80</v>
@@ -26542,10 +26550,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26590,7 +26598,7 @@
         <v>80</v>
       </c>
       <c r="S193" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="T193" t="s" s="2">
         <v>80</v>
@@ -26644,7 +26652,7 @@
         <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>80</v>
@@ -26667,10 +26675,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26693,17 +26701,17 @@
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>80</v>
@@ -26752,7 +26760,7 @@
         <v>80</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>90</v>
@@ -26767,33 +26775,33 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP194" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ194" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26816,17 +26824,17 @@
         <v>80</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>80</v>
@@ -26875,7 +26883,7 @@
         <v>80</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -26902,7 +26910,7 @@
         <v>80</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP195" t="s" s="2">
         <v>80</v>
@@ -26913,13 +26921,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>80</v>
@@ -26941,13 +26949,13 @@
         <v>91</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26998,7 +27006,7 @@
         <v>80</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -27022,10 +27030,10 @@
         <v>80</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>80</v>
@@ -27036,10 +27044,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27157,10 +27165,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27280,14 +27288,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -27309,10 +27317,10 @@
         <v>136</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N199" t="s" s="2">
         <v>139</v>
@@ -27367,7 +27375,7 @@
         <v>80</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -27405,10 +27413,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27434,14 +27442,14 @@
         <v>196</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>80</v>
@@ -27469,10 +27477,10 @@
         <v>200</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>80</v>
@@ -27490,7 +27498,7 @@
         <v>80</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -27514,24 +27522,24 @@
         <v>80</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ200" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27649,10 +27657,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27772,10 +27780,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27820,7 +27828,7 @@
         <v>80</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>80</v>
@@ -27874,7 +27882,7 @@
         <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>80</v>
@@ -27897,10 +27905,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27945,7 +27953,7 @@
         <v>80</v>
       </c>
       <c r="S204" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="T204" t="s" s="2">
         <v>80</v>
@@ -27999,7 +28007,7 @@
         <v>102</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>80</v>
@@ -28022,10 +28030,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28048,17 +28056,17 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>80</v>
@@ -28107,7 +28115,7 @@
         <v>80</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -28122,33 +28130,33 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP205" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ205" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28171,17 +28179,17 @@
         <v>80</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>80</v>
@@ -28230,7 +28238,7 @@
         <v>80</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -28257,7 +28265,7 @@
         <v>80</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>80</v>
@@ -28268,10 +28276,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28294,17 +28302,17 @@
         <v>91</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>80</v>
@@ -28353,7 +28361,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -28365,13 +28373,13 @@
         <v>80</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>80</v>
@@ -28380,10 +28388,10 @@
         <v>80</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AP207" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AQ207" t="s" s="2">
         <v>80</v>
@@ -28391,10 +28399,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28420,13 +28428,13 @@
         <v>196</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -28455,10 +28463,10 @@
         <v>200</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>80</v>
@@ -28476,7 +28484,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28500,13 +28508,13 @@
         <v>80</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AP208" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AQ208" t="s" s="2">
         <v>80</v>
@@ -28514,10 +28522,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28635,10 +28643,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28758,10 +28766,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28883,10 +28891,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28985,10 +28993,10 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>80</v>
@@ -29008,10 +29016,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29034,16 +29042,16 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -29093,7 +29101,7 @@
         <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -29117,13 +29125,13 @@
         <v>80</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AP213" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AQ213" t="s" s="2">
         <v>80</v>
@@ -29131,10 +29139,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29160,13 +29168,13 @@
         <v>196</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -29195,10 +29203,10 @@
         <v>200</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>80</v>
@@ -29216,7 +29224,7 @@
         <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -29243,21 +29251,21 @@
         <v>80</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ214" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29283,13 +29291,13 @@
         <v>196</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -29318,10 +29326,10 @@
         <v>200</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>80</v>
@@ -29339,7 +29347,7 @@
         <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -29366,7 +29374,7 @@
         <v>80</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>80</v>
@@ -29377,10 +29385,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29403,16 +29411,16 @@
         <v>80</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -29462,7 +29470,7 @@
         <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -29489,7 +29497,7 @@
         <v>80</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>80</v>
@@ -29500,10 +29508,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29529,13 +29537,13 @@
         <v>196</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -29564,10 +29572,10 @@
         <v>200</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>80</v>
@@ -29585,7 +29593,7 @@
         <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -29612,7 +29620,7 @@
         <v>80</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>80</v>
@@ -29623,10 +29631,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29744,10 +29752,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29867,10 +29875,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29966,10 +29974,10 @@
         <v>80</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>80</v>
@@ -29992,10 +30000,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30091,10 +30099,10 @@
         <v>80</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>80</v>
@@ -30117,10 +30125,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30143,17 +30151,17 @@
         <v>80</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>80</v>
@@ -30202,7 +30210,7 @@
         <v>80</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -30229,7 +30237,7 @@
         <v>80</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>80</v>
@@ -30240,10 +30248,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30269,10 +30277,10 @@
         <v>196</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -30302,10 +30310,10 @@
         <v>200</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>80</v>
@@ -30323,7 +30331,7 @@
         <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -30350,7 +30358,7 @@
         <v>80</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>80</v>
@@ -30361,10 +30369,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30387,13 +30395,13 @@
         <v>80</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -30444,7 +30452,7 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -30459,7 +30467,7 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>80</v>
@@ -30468,24 +30476,24 @@
         <v>80</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ224" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30508,13 +30516,13 @@
         <v>80</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -30565,7 +30573,7 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30592,7 +30600,7 @@
         <v>80</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>80</v>
@@ -30603,10 +30611,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30724,10 +30732,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30847,14 +30855,14 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
@@ -30876,10 +30884,10 @@
         <v>136</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N228" t="s" s="2">
         <v>139</v>
@@ -30934,7 +30942,7 @@
         <v>80</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -30972,10 +30980,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -31001,10 +31009,10 @@
         <v>196</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -31034,10 +31042,10 @@
         <v>114</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>80</v>
@@ -31055,7 +31063,7 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -31082,7 +31090,7 @@
         <v>80</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="AP229" t="s" s="2">
         <v>80</v>
@@ -31093,10 +31101,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31119,13 +31127,13 @@
         <v>80</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -31176,7 +31184,7 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>90</v>
@@ -31203,7 +31211,7 @@
         <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -31214,10 +31222,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31240,19 +31248,19 @@
         <v>80</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
@@ -31301,7 +31309,7 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -31328,7 +31336,7 @@
         <v>80</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>80</v>
@@ -31339,10 +31347,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31368,13 +31376,13 @@
         <v>196</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -31403,10 +31411,10 @@
         <v>200</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>80</v>
@@ -31424,7 +31432,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31451,7 +31459,7 @@
         <v>80</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1144,7 +1144,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1290:If 130-118 NON-OR PROCEDURE == ‘Y’ then source value from (130-121) {null}psp-25-1292:If 130-118 NON-OR PROCEDURE != ‘Y’ then source value from (130-.22) {null}</t>
+psp-25-1290:If 130-118 NON-OR PROCEDURE == ‘Y’ then source value from (130-121) {true}psp-25-1292:If 130-118 NON-OR PROCEDURE != ‘Y’ then source value from (130-.22) {true}</t>
   </si>
   <si>
     <t>1292: source value based on SURGERY - TIME OPERATION BEGAN (130-.22) if 130-118 NON-OR PROCEDURE != ‘Y’</t>
@@ -1181,7 +1181,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1291:If 130-118 NON-OR PROCEDURE == ‘Y’ then source value from (130-122) {null}psp-25-1293:If 130-118 NON-OR PROCEDURE != ‘Y’ then source value from (130-.23) {null}</t>
+psp-25-1291:If 130-118 NON-OR PROCEDURE == ‘Y’ then source value from (130-122) {true}psp-25-1293:If 130-118 NON-OR PROCEDURE != ‘Y’ then source value from (130-.23) {true}</t>
   </si>
   <si>
     <t>1293: source value based on SURGERY - TIME OPERATION ENDS (130-.23) if 130-118 NON-OR PROCEDURE != ‘Y’</t>
@@ -2201,7 +2201,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1294:If 130-118 NON-OR PROCEDURE == ‘Y’ then reference /Location based on (130-119 &gt; 131.7-) {null}psp-25-1295:If 130-118 NON-OR PROCEDURE != ‘Y’ then reference LocationOR based on (130-.02) {null}</t>
+psp-25-1294:If 130-118 NON-OR PROCEDURE == ‘Y’ then reference /Location based on (130-119 &gt; 131.7-) {true}psp-25-1295:If 130-118 NON-OR PROCEDURE != ‘Y’ then reference LocationOR based on (130-.02) {true}</t>
   </si>
   <si>
     <t>1295: reference based on SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) if 130-118 NON-OR PROCEDURE != ‘Y’</t>
@@ -2376,7 +2376,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1296:If (130-688) is == ‘Y’ then fixed value http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {null}psp-25-1297:If (130-258) is == ‘Y’ then fixed value http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {null}</t>
+psp-25-1296:If (130-688) is == ‘Y’ then fixed value http://snomed.info/sct#88797001 "Complication of surgical procedure (disorder)" {true}psp-25-1297:If (130-258) is == ‘Y’ then fixed value http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" {true}</t>
   </si>
   <si>
     <t>1297: fixed value = http://snomed.info/sct#22298006 "Myocardial infarction (disorder)" when SURGERY - MYOCARDIAL INFARCTION (130-258) if == ‘Y’</t>
@@ -2386,7 +2386,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1296-1:If (undefined) is == ‘Y’ then fixed value STOMA COMPLICATIONS {null}psp-25-1297-1:If (undefined) is == ‘Y’ then fixed value MYOCARDIAL INFARCTION {null}</t>
+psp-25-1296-1:If == ‘Y’ then fixed value STOMA COMPLICATIONS {true}psp-25-1297-1:If == ‘Y’ then fixed value MYOCARDIAL INFARCTION {true}</t>
   </si>
   <si>
     <t>1297-1: fixed value = MYOCARDIAL INFARCTION if == ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2201,7 +2201,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-psp-25-1294:If 130-118 NON-OR PROCEDURE == ‘Y’ then reference /Location based on (130-119 &gt; 131.7-) {true}psp-25-1295:If 130-118 NON-OR PROCEDURE != ‘Y’ then reference LocationOR based on (130-.02) {true}</t>
+psp-25-1294:If 130-118 NON-OR PROCEDURE == ‘Y’ then reference /Location based on (130-119) {true}psp-25-1295:If 130-118 NON-OR PROCEDURE != ‘Y’ then reference LocationOR based on (130-.02) {true}</t>
   </si>
   <si>
     <t>1295: reference based on SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) if 130-118 NON-OR PROCEDURE != ‘Y’</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1350,37 +1350,37 @@
     <t>.scoper</t>
   </si>
   <si>
-    <t>Procedure.performer:va-0</t>
-  </si>
-  <si>
-    <t>va-0</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-0.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-0.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-0.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-0.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-0.function.id</t>
+    <t>Procedure.performer:va-p0</t>
+  </si>
+  <si>
+    <t>va-p0</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p0.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p0.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p0.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p0.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p0.function.id</t>
   </si>
   <si>
     <t>Procedure.performer.function.id</t>
   </si>
   <si>
-    <t>Procedure.performer:va-0.function.extension</t>
+    <t>Procedure.performer:va-p0.function.extension</t>
   </si>
   <si>
     <t>Procedure.performer.function.extension</t>
   </si>
   <si>
-    <t>Procedure.performer:va-0.function.coding</t>
+    <t>Procedure.performer:va-p0.function.coding</t>
   </si>
   <si>
     <t>Procedure.performer.function.coding</t>
@@ -1396,7 +1396,7 @@
     <t>1298-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.167 "PERFUSIONIST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-0.function.text</t>
+    <t>Procedure.performer:va-p0.function.text</t>
   </si>
   <si>
     <t>Procedure.performer.function.text</t>
@@ -1408,7 +1408,7 @@
     <t>1298-1: fixed value = PERFUSIONIST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-0.actor</t>
+    <t>Procedure.performer:va-p0.actor</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
@@ -1421,34 +1421,34 @@
     <t>Surg.SurgeryINTRA.PerfusionistStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-0.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1</t>
-  </si>
-  <si>
-    <t>va-1</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-1.function.coding</t>
+    <t>Procedure.performer:va-p0.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1</t>
+  </si>
+  <si>
+    <t>va-p1</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p1.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1461,7 +1461,7 @@
     <t>1330-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.14 "PRIMARY SURGEON"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-1.function.text</t>
+    <t>Procedure.performer:va-p1.function.text</t>
   </si>
   <si>
     <t>PRIMARY SURGEON</t>
@@ -1470,7 +1470,7 @@
     <t>1330-1: fixed value = PRIMARY SURGEON</t>
   </si>
   <si>
-    <t>Procedure.performer:va-1.actor</t>
+    <t>Procedure.performer:va-p1.actor</t>
   </si>
   <si>
     <t>1330: reference based on SURGERY - PRIMARY SURGEON (130-.14)</t>
@@ -1482,34 +1482,34 @@
     <t>Procedure.Clinician</t>
   </si>
   <si>
-    <t>Procedure.performer:va-1.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2</t>
-  </si>
-  <si>
-    <t>va-2</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-2.function.coding</t>
+    <t>Procedure.performer:va-p1.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2</t>
+  </si>
+  <si>
+    <t>va-p2</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p2.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1522,7 +1522,7 @@
     <t>1331-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.15 "FIRST ASST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-2.function.text</t>
+    <t>Procedure.performer:va-p2.function.text</t>
   </si>
   <si>
     <t>FIRST ASST</t>
@@ -1531,7 +1531,7 @@
     <t>1331-1: fixed value = FIRST ASST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-2.actor</t>
+    <t>Procedure.performer:va-p2.actor</t>
   </si>
   <si>
     <t>1331: reference based on SURGERY - FIRST ASST (130-.15)</t>
@@ -1540,34 +1540,34 @@
     <t>Surg.SurgeryINTRA.FirstAssistingStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-2.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3</t>
-  </si>
-  <si>
-    <t>va-3</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-3.function.coding</t>
+    <t>Procedure.performer:va-p2.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3</t>
+  </si>
+  <si>
+    <t>va-p3</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p3.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1580,7 +1580,7 @@
     <t>1332-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.16 "SECOND ASST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-3.function.text</t>
+    <t>Procedure.performer:va-p3.function.text</t>
   </si>
   <si>
     <t>SECOND ASST</t>
@@ -1589,7 +1589,7 @@
     <t>1332-1: fixed value = SECOND ASST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-3.actor</t>
+    <t>Procedure.performer:va-p3.actor</t>
   </si>
   <si>
     <t>1332: reference based on SURGERY - SECOND ASST (130-.16)</t>
@@ -1598,34 +1598,34 @@
     <t>Surg.SurgeryINTRA.SecondAssistingStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-3.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4</t>
-  </si>
-  <si>
-    <t>va-4</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-4.function.coding</t>
+    <t>Procedure.performer:va-p3.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4</t>
+  </si>
+  <si>
+    <t>va-p4</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p4.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1638,7 +1638,7 @@
     <t>1333-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.164 "ATTENDING SURGEON"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-4.function.text</t>
+    <t>Procedure.performer:va-p4.function.text</t>
   </si>
   <si>
     <t>ATTENDING SURGEON</t>
@@ -1647,7 +1647,7 @@
     <t>1333-1: fixed value = ATTENDING SURGEON</t>
   </si>
   <si>
-    <t>Procedure.performer:va-4.actor</t>
+    <t>Procedure.performer:va-p4.actor</t>
   </si>
   <si>
     <t>1333: reference based on SURGERY - ATTENDING SURGEON (130-.164)</t>
@@ -1659,34 +1659,34 @@
     <t>Procedure.Extension[ProcedureExtension].AttendingClinician</t>
   </si>
   <si>
-    <t>Procedure.performer:va-4.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5</t>
-  </si>
-  <si>
-    <t>va-5</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-5.function.coding</t>
+    <t>Procedure.performer:va-p4.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5</t>
+  </si>
+  <si>
+    <t>va-p5</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p5.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1699,7 +1699,7 @@
     <t>1334-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.168 "ASST PERFUSIONIST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-5.function.text</t>
+    <t>Procedure.performer:va-p5.function.text</t>
   </si>
   <si>
     <t>ASST PERFUSIONIST</t>
@@ -1708,7 +1708,7 @@
     <t>1334-1: fixed value = ASST PERFUSIONIST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-5.actor</t>
+    <t>Procedure.performer:va-p5.actor</t>
   </si>
   <si>
     <t>1334: reference based on SURGERY - ASST PERFUSIONIST (130-.168)</t>
@@ -1717,34 +1717,34 @@
     <t>Surg.SurgeryINTRA.AssistingPerfusionistStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-5.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6</t>
-  </si>
-  <si>
-    <t>va-6</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-6.function.coding</t>
+    <t>Procedure.performer:va-p5.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6</t>
+  </si>
+  <si>
+    <t>va-p6</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p6.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1757,7 +1757,7 @@
     <t>1335-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.18 "SKIN PREPPED BY (1)"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-6.function.text</t>
+    <t>Procedure.performer:va-p6.function.text</t>
   </si>
   <si>
     <t>SKIN PREPPED BY (1)</t>
@@ -1766,7 +1766,7 @@
     <t>1335-1: fixed value = SKIN PREPPED BY (1)</t>
   </si>
   <si>
-    <t>Procedure.performer:va-6.actor</t>
+    <t>Procedure.performer:va-p6.actor</t>
   </si>
   <si>
     <t>1335: reference based on SURGERY - SKIN PREPPED BY (1) (130-.18)</t>
@@ -1775,34 +1775,34 @@
     <t>Surg.SurgeryINTRA.SkinPreparationStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-6.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7</t>
-  </si>
-  <si>
-    <t>va-7</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-7.function.coding</t>
+    <t>Procedure.performer:va-p6.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7</t>
+  </si>
+  <si>
+    <t>va-p7</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p7.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1815,7 +1815,7 @@
     <t>1336-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.31 "PRINC ANESTHETIST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-7.function.text</t>
+    <t>Procedure.performer:va-p7.function.text</t>
   </si>
   <si>
     <t>PRINC ANESTHETIST</t>
@@ -1824,7 +1824,7 @@
     <t>1336-1: fixed value = PRINC ANESTHETIST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-7.actor</t>
+    <t>Procedure.performer:va-p7.actor</t>
   </si>
   <si>
     <t>1336: reference based on SURGERY - PRINC ANESTHETIST (130-.31)</t>
@@ -1833,34 +1833,34 @@
     <t>Surg.SurgeryINTRA.PrincipalAnesthetistStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-7.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8</t>
-  </si>
-  <si>
-    <t>va-8</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-8.function.coding</t>
+    <t>Procedure.performer:va-p7.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8</t>
+  </si>
+  <si>
+    <t>va-p8</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p8.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1873,7 +1873,7 @@
     <t>1337-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.32 "RELIEF ANESTHETIST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-8.function.text</t>
+    <t>Procedure.performer:va-p8.function.text</t>
   </si>
   <si>
     <t>RELIEF ANESTHETIST</t>
@@ -1882,7 +1882,7 @@
     <t>1337-1: fixed value = RELIEF ANESTHETIST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-8.actor</t>
+    <t>Procedure.performer:va-p8.actor</t>
   </si>
   <si>
     <t>1337: reference based on SURGERY - RELIEF ANESTHETIST (130-.32)</t>
@@ -1891,34 +1891,34 @@
     <t>Surg.SurgeryINTRA.ReliefAnesthetistStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-8.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9</t>
-  </si>
-  <si>
-    <t>va-9</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-9.function.coding</t>
+    <t>Procedure.performer:va-p8.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9</t>
+  </si>
+  <si>
+    <t>va-p9</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p9.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1931,7 +1931,7 @@
     <t>1338-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.33 "ASST ANESTHETIST"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-9.function.text</t>
+    <t>Procedure.performer:va-p9.function.text</t>
   </si>
   <si>
     <t>ASST ANESTHETIST</t>
@@ -1940,7 +1940,7 @@
     <t>1338-1: fixed value = ASST ANESTHETIST</t>
   </si>
   <si>
-    <t>Procedure.performer:va-9.actor</t>
+    <t>Procedure.performer:va-p9.actor</t>
   </si>
   <si>
     <t>1338: reference based on SURGERY - ASST ANESTHETIST (130-.33)</t>
@@ -1949,34 +1949,34 @@
     <t>Surg.SurgeryINTRA.AssistingAnesthetistStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-9.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10</t>
-  </si>
-  <si>
-    <t>va-10</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-10.function.coding</t>
+    <t>Procedure.performer:va-p9.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10</t>
+  </si>
+  <si>
+    <t>va-p10</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p10.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1989,7 +1989,7 @@
     <t>1339-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 "ANESTHESIOLOGIST SUPVR"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-10.function.text</t>
+    <t>Procedure.performer:va-p10.function.text</t>
   </si>
   <si>
     <t>ANESTHESIOLOGIST SUPVR</t>
@@ -1998,7 +1998,7 @@
     <t>1339-1: fixed value = ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
-    <t>Procedure.performer:va-10.actor</t>
+    <t>Procedure.performer:va-p10.actor</t>
   </si>
   <si>
     <t>1339: reference based on SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
@@ -2007,34 +2007,34 @@
     <t>Surg.SurgeryINTRA.AnesthesiologistSupervisorStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-10.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11</t>
-  </si>
-  <si>
-    <t>va-11</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-11.function.coding</t>
+    <t>Procedure.performer:va-p10.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11</t>
+  </si>
+  <si>
+    <t>va-p11</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p11.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -2047,7 +2047,7 @@
     <t>1340-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.522 "VERIFIER"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-11.function.text</t>
+    <t>Procedure.performer:va-p11.function.text</t>
   </si>
   <si>
     <t>VERIFIER</t>
@@ -2056,7 +2056,7 @@
     <t>1340-1: fixed value = VERIFIER</t>
   </si>
   <si>
-    <t>Procedure.performer:va-11.actor</t>
+    <t>Procedure.performer:va-p11.actor</t>
   </si>
   <si>
     <t>1340: reference based on SURGERY - VERIFIER (130-.522)</t>
@@ -2065,34 +2065,34 @@
     <t>Surg.SurgeryINTRA.VerifierStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-11.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12</t>
-  </si>
-  <si>
-    <t>va-12</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-12.function.coding</t>
+    <t>Procedure.performer:va-p11.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12</t>
+  </si>
+  <si>
+    <t>va-p12</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p12.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -2105,7 +2105,7 @@
     <t>1341-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#123 "PROVIDER"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-12.function.text</t>
+    <t>Procedure.performer:va-p12.function.text</t>
   </si>
   <si>
     <t>PROVIDER</t>
@@ -2114,7 +2114,7 @@
     <t>1341-1: fixed value = PROVIDER</t>
   </si>
   <si>
-    <t>Procedure.performer:va-12.actor</t>
+    <t>Procedure.performer:va-p12.actor</t>
   </si>
   <si>
     <t>1341: reference based on SURGERY - PROVIDER (130-123)</t>
@@ -2123,34 +2123,34 @@
     <t>Surg.SurgeryINTRA.ProviderIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-12.onBehalfOf</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13</t>
-  </si>
-  <si>
-    <t>va-13</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.function</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.function.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.function.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer:va-13.function.coding</t>
+    <t>Procedure.performer:va-p12.onBehalfOf</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13</t>
+  </si>
+  <si>
+    <t>va-p13</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.function</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.function.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.function.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer:va-p13.function.coding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -2163,7 +2163,7 @@
     <t>1342-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.57 "FOLEY CATHETER INSERTED BY"</t>
   </si>
   <si>
-    <t>Procedure.performer:va-13.function.text</t>
+    <t>Procedure.performer:va-p13.function.text</t>
   </si>
   <si>
     <t>FOLEY CATHETER INSERTED BY</t>
@@ -2172,7 +2172,7 @@
     <t>1342-1: fixed value = FOLEY CATHETER INSERTED BY</t>
   </si>
   <si>
-    <t>Procedure.performer:va-13.actor</t>
+    <t>Procedure.performer:va-p13.actor</t>
   </si>
   <si>
     <t>1342: reference based on SURGERY - FOLEY CATHETER INSERTED BY (130-.57)</t>
@@ -2181,7 +2181,7 @@
     <t>Surg.SurgeryINTRA.FoleyCatheterStaffIEN</t>
   </si>
   <si>
-    <t>Procedure.performer:va-13.onBehalfOf</t>
+    <t>Procedure.performer:va-p13.onBehalfOf</t>
   </si>
   <si>
     <t>Procedure.location</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
